--- a/12604978.xlsx
+++ b/12604978.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL KUMAR\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8490FE09-7A4C-4A04-A09A-427C782C9E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -384,9 +384,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -403,9 +400,12 @@
     <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -891,74 +891,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="22">
         <v>12604978</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1004,54 +1004,54 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
+    <row r="6" spans="1:14" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
         <v>46251</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>360</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <v>30</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>120</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="14">
         <v>90</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="14">
         <v>250</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>5</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>30</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="15">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>880</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="15">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
         <v>560</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="M6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="17" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="A7" s="18">
         <v>46252</v>
       </c>
       <c r="B7" s="9">
@@ -1097,7 +1097,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
+      <c r="A8" s="18">
         <v>46253</v>
       </c>
       <c r="B8" s="9"/>
@@ -1121,7 +1121,7 @@
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
+      <c r="A9" s="18">
         <v>46254</v>
       </c>
       <c r="B9" s="9"/>
@@ -1145,7 +1145,7 @@
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>46255</v>
       </c>
       <c r="B10" s="9"/>
@@ -1169,7 +1169,7 @@
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
+      <c r="A11" s="18">
         <v>46256</v>
       </c>
       <c r="B11" s="9"/>
@@ -1193,7 +1193,7 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
+      <c r="A12" s="18">
         <v>46257</v>
       </c>
       <c r="B12" s="9"/>
@@ -1217,7 +1217,7 @@
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
+      <c r="A13" s="18">
         <v>46258</v>
       </c>
       <c r="B13" s="9"/>
@@ -1241,7 +1241,7 @@
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>46259</v>
       </c>
       <c r="B14" s="9"/>
@@ -1265,7 +1265,7 @@
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
+      <c r="A15" s="18">
         <v>46260</v>
       </c>
       <c r="B15" s="9"/>
@@ -1289,7 +1289,7 @@
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="21">
+      <c r="A16" s="18">
         <v>46261</v>
       </c>
       <c r="B16" s="9"/>
@@ -1313,7 +1313,7 @@
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="21">
+      <c r="A17" s="18">
         <v>46262</v>
       </c>
       <c r="B17" s="9"/>
@@ -1337,7 +1337,7 @@
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
+      <c r="A18" s="18">
         <v>46263</v>
       </c>
       <c r="B18" s="9"/>
@@ -1361,7 +1361,7 @@
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
+      <c r="A19" s="18">
         <v>46264</v>
       </c>
       <c r="B19" s="9"/>
